--- a/static/uploads/2025-2026/master_sheet.xlsx
+++ b/static/uploads/2025-2026/master_sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/690d49f7c0aa36f5/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pallavai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{316B5196-EA75-4D10-A879-C2C5EF29FF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01375714-9937-43C7-B350-564CAB968B1D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58FCC6A-F8C2-4626-B87C-94DCAD2BD36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CB53044-4ACA-476F-BD6F-9B67AAF67AA6}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4922" uniqueCount="1670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="1670">
   <si>
     <t>S. No</t>
   </si>
@@ -12403,7 +12403,9 @@
         <v>1267</v>
       </c>
       <c r="AA87" s="5"/>
-      <c r="AB87" s="5"/>
+      <c r="AB87" s="5" t="s">
+        <v>337</v>
+      </c>
       <c r="AC87" s="5"/>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.3">

--- a/static/uploads/2025-2026/master_sheet.xlsx
+++ b/static/uploads/2025-2026/master_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pallavai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58FCC6A-F8C2-4626-B87C-94DCAD2BD36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F36413-B734-430D-8415-C78AA06CE627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CB53044-4ACA-476F-BD6F-9B67AAF67AA6}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="1670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4924" uniqueCount="1671">
   <si>
     <t>S. No</t>
   </si>
@@ -5151,6 +5151,9 @@
   </si>
   <si>
     <t>AJINKYA SUNIL GAWANDE</t>
+  </si>
+  <si>
+    <t>IBM</t>
   </si>
 </sst>
 </file>
@@ -7036,7 +7039,7 @@
         <v>762</v>
       </c>
       <c r="S18" s="4">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="T18" s="4">
         <v>0</v>
@@ -7060,7 +7063,9 @@
         <v>1202</v>
       </c>
       <c r="AA18" s="5"/>
-      <c r="AB18" s="5"/>
+      <c r="AB18" s="5" t="s">
+        <v>1670</v>
+      </c>
       <c r="AC18" s="5"/>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.3">

--- a/static/uploads/2025-2026/master_sheet.xlsx
+++ b/static/uploads/2025-2026/master_sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pallavai\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/690d49f7c0aa36f5/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F36413-B734-430D-8415-C78AA06CE627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{316B5196-EA75-4D10-A879-C2C5EF29FF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E5FBE9-19DB-4051-8AA6-8311CF51B208}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CB53044-4ACA-476F-BD6F-9B67AAF67AA6}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4924" uniqueCount="1671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4921" uniqueCount="1670">
   <si>
     <t>S. No</t>
   </si>
@@ -5151,9 +5151,6 @@
   </si>
   <si>
     <t>AJINKYA SUNIL GAWANDE</t>
-  </si>
-  <si>
-    <t>IBM</t>
   </si>
 </sst>
 </file>
@@ -5304,6 +5301,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5633,8 +5634,8 @@
     <col min="5" max="7" width="18.88671875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="37.5546875" customWidth="1"/>
-    <col min="10" max="10" width="109" style="14" customWidth="1"/>
-    <col min="11" max="11" width="21.88671875" customWidth="1"/>
+    <col min="10" max="10" width="140.77734375" style="14" customWidth="1"/>
+    <col min="11" max="11" width="29.109375" customWidth="1"/>
     <col min="12" max="12" width="23.21875" customWidth="1"/>
     <col min="13" max="14" width="28.109375" customWidth="1"/>
     <col min="15" max="15" width="37.5546875" customWidth="1"/>
@@ -7039,7 +7040,7 @@
         <v>762</v>
       </c>
       <c r="S18" s="4">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="T18" s="4">
         <v>0</v>
@@ -7063,9 +7064,7 @@
         <v>1202</v>
       </c>
       <c r="AA18" s="5"/>
-      <c r="AB18" s="5" t="s">
-        <v>1670</v>
-      </c>
+      <c r="AB18" s="5"/>
       <c r="AC18" s="5"/>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.3">
@@ -12408,9 +12407,7 @@
         <v>1267</v>
       </c>
       <c r="AA87" s="5"/>
-      <c r="AB87" s="5" t="s">
-        <v>337</v>
-      </c>
+      <c r="AB87" s="5"/>
       <c r="AC87" s="5"/>
     </row>
     <row r="88" spans="1:29" x14ac:dyDescent="0.3">
@@ -32283,8 +32280,8 @@
       <c r="S344" s="4">
         <v>8.73</v>
       </c>
-      <c r="T344" s="9" t="s">
-        <v>777</v>
+      <c r="T344" s="9">
+        <v>0</v>
       </c>
       <c r="U344" s="4" t="s">
         <v>336</v>

--- a/static/uploads/2025-2026/master_sheet.xlsx
+++ b/static/uploads/2025-2026/master_sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/690d49f7c0aa36f5/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pallavai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{316B5196-EA75-4D10-A879-C2C5EF29FF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E5FBE9-19DB-4051-8AA6-8311CF51B208}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2D40F9-0D87-46DA-BB1C-1AAB67BD5592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CB53044-4ACA-476F-BD6F-9B67AAF67AA6}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4921" uniqueCount="1670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="1671">
   <si>
     <t>S. No</t>
   </si>
@@ -5151,6 +5151,9 @@
   </si>
   <si>
     <t>AJINKYA SUNIL GAWANDE</t>
+  </si>
+  <si>
+    <t>Google</t>
   </si>
 </sst>
 </file>
@@ -5301,10 +5304,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11705,7 +11704,9 @@
       <c r="Z78" s="2" t="s">
         <v>1260</v>
       </c>
-      <c r="AA78" s="5"/>
+      <c r="AA78" s="5" t="s">
+        <v>1670</v>
+      </c>
       <c r="AB78" s="5"/>
       <c r="AC78" s="5"/>
     </row>
@@ -12483,7 +12484,9 @@
       <c r="Z88" s="2" t="s">
         <v>1268</v>
       </c>
-      <c r="AA88" s="5"/>
+      <c r="AA88" s="5" t="s">
+        <v>1670</v>
+      </c>
       <c r="AB88" s="5"/>
       <c r="AC88" s="5"/>
     </row>

--- a/static/uploads/2025-2026/master_sheet.xlsx
+++ b/static/uploads/2025-2026/master_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pallavai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2D40F9-0D87-46DA-BB1C-1AAB67BD5592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0E2A0F-2C43-44FD-991D-7152303F5234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CB53044-4ACA-476F-BD6F-9B67AAF67AA6}"/>
   </bookViews>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="1671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4922" uniqueCount="1671">
   <si>
     <t>S. No</t>
   </si>
@@ -12484,9 +12484,7 @@
       <c r="Z88" s="2" t="s">
         <v>1268</v>
       </c>
-      <c r="AA88" s="5" t="s">
-        <v>1670</v>
-      </c>
+      <c r="AA88" s="5"/>
       <c r="AB88" s="5"/>
       <c r="AC88" s="5"/>
     </row>

--- a/static/uploads/2025-2026/master_sheet.xlsx
+++ b/static/uploads/2025-2026/master_sheet.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/690d49f7c0aa36f5/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pallavai\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E1A5E9B7-966A-4DD4-8614-1B0B9871B3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55DFBD50-56FF-4EB8-A39C-7C79411C90B1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951B9182-D6C0-4B18-8DBD-10114B20E959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7936B978-1816-4CAC-9AA1-03C7CDB85C9C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>S. No</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>129004317@sastra.ac.in</t>
+  </si>
+  <si>
+    <t>google</t>
   </si>
 </sst>
 </file>
@@ -266,10 +269,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -791,6 +790,9 @@
       <c r="Z2" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="AA2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3">
